--- a/Pasta6.xlsx
+++ b/Pasta6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\ErickDias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11AD94E2-DE8B-43D9-94D2-CBECED1E78D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B386908-8A4A-4D88-9DBB-61223780C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{829081F7-2D92-4F09-A52B-DDA93CFE2C5E}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -178,13 +178,7 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -202,6 +196,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -528,236 +528,236 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>6.25</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>7.25</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>6</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>7.8</v>
       </c>
-      <c r="F4" s="3">
-        <f>B4/4+C4/4+D4/4+E4/4</f>
+      <c r="F4" s="1">
+        <f>(B4+C4+D4+E4)/4</f>
         <v>6.8250000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>5.5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>6</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
-        <f>B5/4+C5/4+D5/4+E5/4</f>
+      <c r="F5" s="1">
+        <f>(B5+C5+D5+E5)/4</f>
         <v>5.375</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>6.25</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>5.25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>8.25</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>7</v>
       </c>
-      <c r="F6" s="3">
-        <f>B6/4+C6/4+D6/4+E6/4</f>
+      <c r="F6" s="1">
+        <f>(B6+C6+D6+E6)/4</f>
         <v>6.6875</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>5.5</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>8</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>6.5</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>7.25</v>
       </c>
-      <c r="F7" s="3">
-        <f>B7/4+C7/4+D7/4+E7/4</f>
+      <c r="F7" s="1">
+        <f>(B7+C7+D7+E7)/4</f>
         <v>6.8125</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <v>7</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>9.5</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>8.25</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>7</v>
       </c>
-      <c r="F8" s="3">
-        <f>B8/4+C8/4+D8/4+E8/4</f>
+      <c r="F8" s="1">
+        <f>(B8+C8+D8+E8)/4</f>
         <v>7.9375</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>9.25</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>8</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>9</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>10</v>
       </c>
-      <c r="F9" s="3">
-        <f>B9/4+C9/4+D9/4+E9/4</f>
+      <c r="F9" s="1">
+        <f>(B9+C9+D9+E9)/4</f>
         <v>9.0625</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>9.5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>5</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>8</v>
       </c>
-      <c r="F10" s="3">
-        <f>B10/4+C10/4+D10/4+E10/4</f>
+      <c r="F10" s="1">
+        <f>(B10+C10+D10+E10)/4</f>
         <v>7.625</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="3">
         <v>7.25</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>8.25</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>6.5</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>9.25</v>
       </c>
-      <c r="F11" s="3">
-        <f>B11/4+C11/4+D11/4+E11/4</f>
+      <c r="F11" s="1">
+        <f>(B11+C11+D11+E11)/4</f>
         <v>7.8125</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>8.25</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>7</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>9.5</v>
       </c>
-      <c r="F12" s="3">
-        <f>B12/4+C12/4+D12/4+E12/4</f>
+      <c r="F12" s="1">
+        <f>(B12+C12+D12+E12)/4</f>
         <v>8.6875</v>
       </c>
     </row>
